--- a/raw_sample_means.xlsx
+++ b/raw_sample_means.xlsx
@@ -1452,7 +1452,7 @@
         <v>9.19382901204416</v>
       </c>
       <c r="E65" t="n">
-        <v>5.437878269521523</v>
+        <v>5.437878269521522</v>
       </c>
     </row>
     <row r="66">
